--- a/output/pdf_financials_xlsx/NKG.xlsx
+++ b/output/pdf_financials_xlsx/NKG.xlsx
@@ -6029,46 +6029,46 @@
         <v>0.383173</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.459473</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.459473</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.459473</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.498873</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.498873</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.498873</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>2.102198</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>2.433604</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>2.010407</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>2.010407</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>5.914944</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>6.081906</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>8.015808</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>9.14273</v>
       </c>
     </row>
     <row r="93">
@@ -9900,7 +9900,11 @@
           <t>Reserves 5</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -10870,7 +10874,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
@@ -12686,7 +12694,11 @@
           <t>Reserves 5</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>-</t>
@@ -13272,7 +13284,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>-</t>
@@ -15355,7 +15371,11 @@
           <t>Share-based payment reserve (Note 6)</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
           <t>-</t>
@@ -16036,7 +16056,11 @@
           <t>Share‐based payment reserve (Note 6)</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/NKG.xlsx
+++ b/output/pdf_financials_xlsx/NKG.xlsx
@@ -1071,10 +1071,10 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.01828</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.000885</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
@@ -1095,25 +1095,25 @@
         <v>0</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.056245</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.014356</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.423069</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.405406</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.11298</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.202176</v>
       </c>
     </row>
     <row r="13">
@@ -2079,10 +2079,10 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.194593</v>
+        <v>-0.212873</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.258622</v>
+        <v>-0.259507</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-0.14451</v>
@@ -2103,25 +2103,25 @@
         <v>-9.487206</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-2.54916</v>
+        <v>-2.605405</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>-1.956228</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-6.89276</v>
+        <v>-6.907116</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-53.589604</v>
+        <v>-54.012673</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-27.013835</v>
+        <v>-27.419241</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-14.999903</v>
+        <v>-15.112883</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-10.409879</v>
+        <v>-10.612055</v>
       </c>
     </row>
     <row r="28">
@@ -2203,10 +2203,10 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.194593</v>
+        <v>-0.212873</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.258622</v>
+        <v>-0.259507</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-0.14451</v>
@@ -2227,25 +2227,25 @@
         <v>-9.487206</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-2.54916</v>
+        <v>-2.605405</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>-1.956228</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-6.871248</v>
+        <v>-6.885604</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-53.552465</v>
+        <v>-53.975534</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-26.968381</v>
+        <v>-27.373787</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-14.985005</v>
+        <v>-15.097985</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-10.409879</v>
+        <v>-10.612055</v>
       </c>
     </row>
     <row r="30">
@@ -2508,55 +2508,55 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.011517</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>5.546937</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.007362</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.45347</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.390062</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.237503</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.092323</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.433244</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.943877</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>1.658615</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>1.664164</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.987697</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>13.153096</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>7.931428</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>5.448406</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>3.28868</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>4.335584</v>
       </c>
     </row>
     <row r="35">
@@ -2624,55 +2624,55 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.011517</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>5.546937</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.007362</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.45347</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.390062</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.237503</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.092323</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.433244</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.943877</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>3</v>
+        <v>4.658615</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>1.664164</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.987697</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>13.153096</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>7.931428</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>5.448406</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>3.28868</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>4.335584</v>
       </c>
     </row>
     <row r="37">
@@ -3320,13 +3320,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.575933</v>
+        <v>0.564416</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>5.599309</v>
+        <v>0.052372</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.049461</v>
+        <v>0.042099</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0</v>
@@ -3344,31 +3344,31 @@
         <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.191181</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>1.800722</v>
+        <v>0.142107</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>1.691623</v>
+        <v>0.027459</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>19.085043</v>
+        <v>18.097346</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>13.953586</v>
+        <v>0.80049</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>8.114953</v>
+        <v>0.183525</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>5.595673</v>
+        <v>0.147267</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>3.466731</v>
+        <v>0.178051</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>4.724424</v>
+        <v>0.38884</v>
       </c>
     </row>
     <row r="49">
@@ -8879,7 +8879,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -14995,7 +14995,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -16365,7 +16365,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E78" s="5" t="n">
@@ -38483,7 +38483,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
@@ -39669,7 +39669,7 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
@@ -42657,7 +42657,7 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
@@ -48263,7 +48263,7 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">

--- a/output/pdf_financials_xlsx/NKG.xlsx
+++ b/output/pdf_financials_xlsx/NKG.xlsx
@@ -782,28 +782,28 @@
         <v>0.064556</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.031868</v>
+        <v>0.349978</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.439027</v>
+        <v>1.934882</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.363814</v>
+        <v>1.75173</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0.522025</v>
+        <v>1.493493</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>0.267335</v>
+        <v>2.219949</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0.19283</v>
+        <v>3.23155</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.326131</v>
+        <v>1.871718</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.512582</v>
+        <v>2.732815</v>
       </c>
     </row>
     <row r="8">
@@ -968,7 +968,7 @@
         <v>0.064556</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.087868</v>
+        <v>0.405978</v>
       </c>
       <c r="L10" s="3" t="n">
         <v>2.58894</v>
@@ -1030,7 +1030,7 @@
         <v>-0.064556</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-0.087868</v>
+        <v>-0.405978</v>
       </c>
       <c r="L11" s="3" t="n">
         <v>-2.58894</v>
@@ -1627,7 +1627,7 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>-0.092471</v>
+        <v>-0.139846</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>-0.258622</v>
@@ -6534,10 +6534,10 @@
         <v>0</v>
       </c>
       <c r="K101" s="3" t="n">
-        <v>0</v>
+        <v>-0.018597</v>
       </c>
       <c r="L101" s="3" t="n">
-        <v>0</v>
+        <v>0.006623</v>
       </c>
       <c r="M101" s="3" t="n">
         <v>-0.058388</v>
@@ -6844,10 +6844,10 @@
         <v>-0.089367</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>-0.088731</v>
+        <v>-0.107328</v>
       </c>
       <c r="L106" s="3" t="n">
-        <v>0.239113</v>
+        <v>0.245736</v>
       </c>
       <c r="M106" s="3" t="n">
         <v>0.063996</v>
@@ -8745,7 +8745,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U410"/>
+  <dimension ref="A1:U419"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -30027,7 +30027,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr"/>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E214" t="inlineStr">
         <is>
           <t>-</t>
@@ -31138,7 +31142,11 @@
           <t>Decrease (increase) in GST receivable</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr"/>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E225" t="inlineStr">
         <is>
           <t>-</t>
@@ -32053,7 +32061,11 @@
           <t>Issuance of common shares in private placement</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr"/>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr">
         <is>
           <t>-</t>
@@ -33071,7 +33083,11 @@
           <t>(Increase) in GST receivable</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr"/>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E244" t="inlineStr">
         <is>
           <t>-</t>
@@ -37324,34 +37340,30 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Depletion and depreciation                                         10,732                  1,063,405</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Exploration and evaluation 4</t>
+          <t>Accretion (note</t>
         </is>
       </c>
       <c r="D286" t="inlineStr"/>
-      <c r="E286" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E286" s="5" t="n">
+        <v>0.062806</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G286" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G286" s="5" t="n">
+        <v>7e-06</v>
       </c>
       <c r="H286" t="inlineStr">
         <is>
@@ -37413,44 +37425,48 @@
           <t>-</t>
         </is>
       </c>
-      <c r="T286" s="5" t="n">
-        <v>9.207822999999999</v>
-      </c>
-      <c r="U286" s="5" t="n">
-        <v>5.419389</v>
+      <c r="T286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Depletion and depreciation                                         10,732                  1,063,405</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Management and director fees 6</t>
-        </is>
-      </c>
-      <c r="D287" t="inlineStr"/>
-      <c r="E287" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Future income tax recovery (note</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
+      <c r="E287" s="5" t="n">
+        <v>-3.045203</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G287" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G287" s="5" t="n">
+        <v>7e-06</v>
       </c>
       <c r="H287" t="inlineStr">
         <is>
@@ -37487,61 +37503,67 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O287" s="5" t="n">
-        <v>1.495855</v>
-      </c>
-      <c r="P287" s="5" t="n">
-        <v>1.387916</v>
+      <c r="O287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q287" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R287" s="5" t="n">
-        <v>1.952614</v>
-      </c>
-      <c r="S287" s="5" t="n">
-        <v>3.03872</v>
-      </c>
-      <c r="T287" s="5" t="n">
-        <v>1.545587</v>
-      </c>
-      <c r="U287" s="5" t="n">
-        <v>2.220233</v>
+      <c r="R287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>(81,739)                 (2,216,821)</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Stock-based payments 5, 6</t>
+          <t>Change in non-cash working capital – operating (note</t>
         </is>
       </c>
       <c r="D288" t="inlineStr"/>
-      <c r="E288" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F288" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G288" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E288" s="5" t="n">
+        <v>0.6079329999999999</v>
+      </c>
+      <c r="F288" s="5" t="n">
+        <v>-0.390833</v>
+      </c>
+      <c r="G288" s="5" t="n">
+        <v>1e-05</v>
       </c>
       <c r="H288" t="inlineStr">
         <is>
@@ -37603,48 +37625,44 @@
           <t>-</t>
         </is>
       </c>
-      <c r="T288" s="5" t="n">
-        <v>1.933902</v>
-      </c>
-      <c r="U288" s="5" t="n">
-        <v>1.126922</v>
+      <c r="T288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Marketing</t>
-        </is>
-      </c>
-      <c r="D289" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
-      <c r="E289" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Proceeds on exercise of stock options (note</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr"/>
+      <c r="E289" s="5" t="n">
+        <v>0.102875</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G289" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G289" s="5" t="n">
+        <v>6e-06</v>
       </c>
       <c r="H289" t="inlineStr">
         <is>
@@ -37686,60 +37704,62 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P289" s="5" t="n">
-        <v>0.069582</v>
-      </c>
-      <c r="Q289" s="5" t="n">
-        <v>0.768555</v>
-      </c>
-      <c r="R289" s="5" t="n">
-        <v>0.526653</v>
-      </c>
-      <c r="S289" s="5" t="n">
-        <v>0.5657</v>
-      </c>
-      <c r="T289" s="5" t="n">
-        <v>0.376967</v>
-      </c>
-      <c r="U289" s="5" t="n">
-        <v>0.688597</v>
+      <c r="P289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Decrease in bank indebtedness                                                                -                  (3,525,000)</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Consulting fees</t>
-        </is>
-      </c>
-      <c r="D290" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E290" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F290" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G290" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Dividends declared (note</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr"/>
+      <c r="E290" s="5" t="n">
+        <v>-8.340164</v>
+      </c>
+      <c r="F290" s="5" t="n">
+        <v>-2.607051</v>
+      </c>
+      <c r="G290" s="5" t="n">
+        <v>6e-06</v>
       </c>
       <c r="H290" t="inlineStr">
         <is>
@@ -37776,63 +37796,69 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O290" s="5" t="n">
-        <v>0.276</v>
-      </c>
-      <c r="P290" s="5" t="n">
-        <v>0.330948</v>
-      </c>
-      <c r="Q290" s="5" t="n">
-        <v>0.394022</v>
-      </c>
-      <c r="R290" s="5" t="n">
-        <v>0.108637</v>
-      </c>
-      <c r="S290" s="5" t="n">
-        <v>0.10595</v>
-      </c>
-      <c r="T290" s="5" t="n">
-        <v>0.181895</v>
-      </c>
-      <c r="U290" s="5" t="n">
-        <v>0.326923</v>
+      <c r="O290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Investing Activities</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Professional fees</t>
-        </is>
-      </c>
-      <c r="D291" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E291" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Expenditures on property and equipment (note</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr"/>
+      <c r="E291" s="5" t="n">
+        <v>-0.119681</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G291" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G291" s="5" t="n">
+        <v>4e-06</v>
       </c>
       <c r="H291" t="inlineStr">
         <is>
@@ -37869,59 +37895,67 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O291" s="5" t="n">
-        <v>0.058746</v>
-      </c>
-      <c r="P291" s="5" t="n">
-        <v>0.045641</v>
-      </c>
-      <c r="Q291" s="5" t="n">
-        <v>0.224994</v>
-      </c>
-      <c r="R291" s="5" t="n">
-        <v>0.311492</v>
-      </c>
-      <c r="S291" s="5" t="n">
-        <v>0.406699</v>
-      </c>
-      <c r="T291" s="5" t="n">
-        <v>0.271653</v>
-      </c>
-      <c r="U291" s="5" t="n">
-        <v>0.267164</v>
+      <c r="O291" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P291" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q291" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R291" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S291" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T291" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U291" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Investing Activities</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Office and sundry</t>
+          <t>Change in non-cash working capital – investing (note</t>
         </is>
       </c>
       <c r="D292" t="inlineStr"/>
-      <c r="E292" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F292" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G292" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E292" s="5" t="n">
+        <v>2.077492</v>
+      </c>
+      <c r="F292" s="5" t="n">
+        <v>-2.459952</v>
+      </c>
+      <c r="G292" s="5" t="n">
+        <v>1e-05</v>
       </c>
       <c r="H292" t="inlineStr">
         <is>
@@ -37958,26 +37992,40 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O292" s="5" t="n">
-        <v>0.166406</v>
-      </c>
-      <c r="P292" s="5" t="n">
-        <v>0.076409</v>
-      </c>
-      <c r="Q292" s="5" t="n">
-        <v>0.278756</v>
-      </c>
-      <c r="R292" s="5" t="n">
-        <v>0.369406</v>
-      </c>
-      <c r="S292" s="5" t="n">
-        <v>0.307248</v>
-      </c>
-      <c r="T292" s="5" t="n">
-        <v>0.254462</v>
-      </c>
-      <c r="U292" s="5" t="n">
-        <v>0.230142</v>
+      <c r="O292" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P292" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q292" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R292" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S292" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T292" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U292" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="293">
@@ -37993,14 +38041,10 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Transfer agent and regulatory fees</t>
-        </is>
-      </c>
-      <c r="D293" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Exploration and evaluation 4</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr"/>
       <c r="E293" t="inlineStr">
         <is>
           <t>-</t>
@@ -38051,26 +38095,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O293" s="5" t="n">
-        <v>0.05804</v>
-      </c>
-      <c r="P293" s="5" t="n">
-        <v>0.032866</v>
-      </c>
-      <c r="Q293" s="5" t="n">
-        <v>0.080124</v>
-      </c>
-      <c r="R293" s="5" t="n">
-        <v>0.083408</v>
-      </c>
-      <c r="S293" s="5" t="n">
-        <v>0.069207</v>
+      <c r="O293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="T293" s="5" t="n">
-        <v>0.088287</v>
+        <v>9.207822999999999</v>
       </c>
       <c r="U293" s="5" t="n">
-        <v>0.102077</v>
+        <v>5.419389</v>
       </c>
     </row>
     <row r="294">
@@ -38086,7 +38140,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Travel</t>
+          <t>Management and director fees 6</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -38145,27 +38199,27 @@
         </is>
       </c>
       <c r="O294" s="5" t="n">
-        <v>0.104987</v>
-      </c>
-      <c r="P294" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q294" s="5" t="n">
-        <v>0.047879</v>
+        <v>1.495855</v>
+      </c>
+      <c r="P294" s="5" t="n">
+        <v>1.387916</v>
+      </c>
+      <c r="Q294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R294" s="5" t="n">
-        <v>0.07529</v>
+        <v>1.952614</v>
       </c>
       <c r="S294" s="5" t="n">
-        <v>0.017673</v>
+        <v>3.03872</v>
       </c>
       <c r="T294" s="5" t="n">
-        <v>0.055949</v>
+        <v>1.545587</v>
       </c>
       <c r="U294" s="5" t="n">
-        <v>0.083582</v>
+        <v>2.220233</v>
       </c>
     </row>
     <row r="295">
@@ -38181,7 +38235,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Depreciation expense</t>
+          <t>Stock-based payments 5, 6</t>
         </is>
       </c>
       <c r="D295" t="inlineStr"/>
@@ -38261,12 +38315,10 @@
         </is>
       </c>
       <c r="T295" s="5" t="n">
-        <v>0.014898</v>
-      </c>
-      <c r="U295" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.933902</v>
+      </c>
+      <c r="U295" s="5" t="n">
+        <v>1.126922</v>
       </c>
     </row>
     <row r="296">
@@ -38282,12 +38334,12 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>EXPENSES total</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
+          <t>OtherOperatingExpenses</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -38340,26 +38392,28 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O296" s="5" t="n">
-        <v>2.58894</v>
+      <c r="O296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P296" s="5" t="n">
-        <v>1.943362</v>
+        <v>0.069582</v>
       </c>
       <c r="Q296" s="5" t="n">
-        <v>7.025051</v>
+        <v>0.768555</v>
       </c>
       <c r="R296" s="5" t="n">
-        <v>23.394774</v>
+        <v>0.526653</v>
       </c>
       <c r="S296" s="5" t="n">
-        <v>27.242541</v>
+        <v>0.5657</v>
       </c>
       <c r="T296" s="5" t="n">
-        <v>13.931423</v>
+        <v>0.376967</v>
       </c>
       <c r="U296" s="5" t="n">
-        <v>10.465029</v>
+        <v>0.688597</v>
       </c>
     </row>
     <row r="297">
@@ -38370,17 +38424,17 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Other (expense) income</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Foreign exchange (loss) gain</t>
+          <t>Consulting fees</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -38433,36 +38487,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O297" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P297" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q297" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R297" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S297" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O297" s="5" t="n">
+        <v>0.276</v>
+      </c>
+      <c r="P297" s="5" t="n">
+        <v>0.330948</v>
+      </c>
+      <c r="Q297" s="5" t="n">
+        <v>0.394022</v>
+      </c>
+      <c r="R297" s="5" t="n">
+        <v>0.108637</v>
+      </c>
+      <c r="S297" s="5" t="n">
+        <v>0.10595</v>
       </c>
       <c r="T297" s="5" t="n">
-        <v>0.035002</v>
+        <v>0.181895</v>
       </c>
       <c r="U297" s="5" t="n">
-        <v>-0.147026</v>
+        <v>0.326923</v>
       </c>
     </row>
     <row r="298">
@@ -38473,17 +38517,17 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Other (expense) income</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Interest income</t>
+          <t>Professional fees</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>InterestIncomeNonOperating</t>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
@@ -38536,36 +38580,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O298" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P298" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q298" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R298" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S298" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O298" s="5" t="n">
+        <v>0.058746</v>
+      </c>
+      <c r="P298" s="5" t="n">
+        <v>0.045641</v>
+      </c>
+      <c r="Q298" s="5" t="n">
+        <v>0.224994</v>
+      </c>
+      <c r="R298" s="5" t="n">
+        <v>0.311492</v>
+      </c>
+      <c r="S298" s="5" t="n">
+        <v>0.406699</v>
       </c>
       <c r="T298" s="5" t="n">
-        <v>0.11298</v>
+        <v>0.271653</v>
       </c>
       <c r="U298" s="5" t="n">
-        <v>0.202176</v>
+        <v>0.267164</v>
       </c>
     </row>
     <row r="299">
@@ -38576,12 +38610,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Other (expense) income</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Loss on spin out of assets 3</t>
+          <t>Office and sundry</t>
         </is>
       </c>
       <c r="D299" t="inlineStr"/>
@@ -38635,38 +38669,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O299" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P299" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q299" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R299" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S299" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O299" s="5" t="n">
+        <v>0.166406</v>
+      </c>
+      <c r="P299" s="5" t="n">
+        <v>0.076409</v>
+      </c>
+      <c r="Q299" s="5" t="n">
+        <v>0.278756</v>
+      </c>
+      <c r="R299" s="5" t="n">
+        <v>0.369406</v>
+      </c>
+      <c r="S299" s="5" t="n">
+        <v>0.307248</v>
       </c>
       <c r="T299" s="5" t="n">
-        <v>-1.216462</v>
-      </c>
-      <c r="U299" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.254462</v>
+      </c>
+      <c r="U299" s="5" t="n">
+        <v>0.230142</v>
       </c>
     </row>
     <row r="300">
@@ -38677,15 +38699,19 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Other (expense) income</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Other (expense) income total</t>
-        </is>
-      </c>
-      <c r="D300" t="inlineStr"/>
+          <t>Transfer agent and regulatory fees</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E300" t="inlineStr">
         <is>
           <t>-</t>
@@ -38736,36 +38762,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O300" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P300" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q300" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R300" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S300" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O300" s="5" t="n">
+        <v>0.05804</v>
+      </c>
+      <c r="P300" s="5" t="n">
+        <v>0.032866</v>
+      </c>
+      <c r="Q300" s="5" t="n">
+        <v>0.080124</v>
+      </c>
+      <c r="R300" s="5" t="n">
+        <v>0.083408</v>
+      </c>
+      <c r="S300" s="5" t="n">
+        <v>0.069207</v>
       </c>
       <c r="T300" s="5" t="n">
-        <v>-1.06848</v>
+        <v>0.088287</v>
       </c>
       <c r="U300" s="5" t="n">
-        <v>0.05515</v>
+        <v>0.102077</v>
       </c>
     </row>
     <row r="301">
@@ -38776,17 +38792,17 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Other (expense) income</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year</t>
+          <t>Travel</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -38839,36 +38855,28 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O301" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O301" s="5" t="n">
+        <v>0.104987</v>
       </c>
       <c r="P301" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q301" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R301" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S301" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q301" s="5" t="n">
+        <v>0.047879</v>
+      </c>
+      <c r="R301" s="5" t="n">
+        <v>0.07529</v>
+      </c>
+      <c r="S301" s="5" t="n">
+        <v>0.017673</v>
       </c>
       <c r="T301" s="5" t="n">
-        <v>-14.999903</v>
+        <v>0.055949</v>
       </c>
       <c r="U301" s="5" t="n">
-        <v>-10.409879</v>
+        <v>0.083582</v>
       </c>
     </row>
     <row r="302">
@@ -38879,12 +38887,12 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Other (expense) income</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per common shares</t>
+          <t>Depreciation expense</t>
         </is>
       </c>
       <c r="D302" t="inlineStr"/>
@@ -38964,10 +38972,12 @@
         </is>
       </c>
       <c r="T302" s="5" t="n">
-        <v>-2.1e-07</v>
-      </c>
-      <c r="U302" s="5" t="n">
-        <v>-1.2e-07</v>
+        <v>0.014898</v>
+      </c>
+      <c r="U302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="303">
@@ -38978,15 +38988,19 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Weighted average number of common</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Weighted average number of common total</t>
-        </is>
-      </c>
-      <c r="D303" t="inlineStr"/>
+          <t>EXPENSES total</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E303" t="inlineStr">
         <is>
           <t>-</t>
@@ -39037,36 +39051,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O303" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P303" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q303" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R303" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S303" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O303" s="5" t="n">
+        <v>2.58894</v>
+      </c>
+      <c r="P303" s="5" t="n">
+        <v>1.943362</v>
+      </c>
+      <c r="Q303" s="5" t="n">
+        <v>7.025051</v>
+      </c>
+      <c r="R303" s="5" t="n">
+        <v>23.394774</v>
+      </c>
+      <c r="S303" s="5" t="n">
+        <v>27.242541</v>
       </c>
       <c r="T303" s="5" t="n">
-        <v>71.33617599999999</v>
+        <v>13.931423</v>
       </c>
       <c r="U303" s="5" t="n">
-        <v>84.264438</v>
+        <v>10.465029</v>
       </c>
     </row>
     <row r="304">
@@ -39077,15 +39081,19 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Other (expense) income</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Depreciation expense 5</t>
-        </is>
-      </c>
-      <c r="D304" t="inlineStr"/>
+          <t>Foreign exchange (loss) gain</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E304" t="inlineStr">
         <is>
           <t>-</t>
@@ -39146,22 +39154,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q304" s="5" t="n">
-        <v>0.021512</v>
-      </c>
-      <c r="R304" s="5" t="n">
-        <v>0.037139</v>
-      </c>
-      <c r="S304" s="5" t="n">
-        <v>0.045454</v>
+      <c r="Q304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="T304" s="5" t="n">
-        <v>0.014898</v>
-      </c>
-      <c r="U304" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.035002</v>
+      </c>
+      <c r="U304" s="5" t="n">
+        <v>-0.147026</v>
       </c>
     </row>
     <row r="305">
@@ -39172,15 +39184,19 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Other (expense) income</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Exploration and evaluation costs 4</t>
-        </is>
-      </c>
-      <c r="D305" t="inlineStr"/>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
       <c r="E305" t="inlineStr">
         <is>
           <t>-</t>
@@ -39241,22 +39257,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q305" s="5" t="n">
-        <v>4.237741</v>
-      </c>
-      <c r="R305" s="5" t="n">
-        <v>16.025598</v>
-      </c>
-      <c r="S305" s="5" t="n">
-        <v>22.405903</v>
+      <c r="Q305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="T305" s="5" t="n">
-        <v>9.207822999999999</v>
-      </c>
-      <c r="U305" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.11298</v>
+      </c>
+      <c r="U305" s="5" t="n">
+        <v>0.202176</v>
       </c>
     </row>
     <row r="306">
@@ -39267,12 +39287,12 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Other (expense) income</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Management and director fees 7</t>
+          <t>Loss on spin out of assets 3</t>
         </is>
       </c>
       <c r="D306" t="inlineStr"/>
@@ -39331,20 +39351,28 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P306" s="5" t="n">
-        <v>1.387916</v>
-      </c>
-      <c r="Q306" s="5" t="n">
-        <v>0.971468</v>
-      </c>
-      <c r="R306" s="5" t="n">
-        <v>1.952614</v>
-      </c>
-      <c r="S306" s="5" t="n">
-        <v>3.03872</v>
+      <c r="P306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="T306" s="5" t="n">
-        <v>1.545587</v>
+        <v>-1.216462</v>
       </c>
       <c r="U306" t="inlineStr">
         <is>
@@ -39360,12 +39388,12 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Other (expense) income</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Stock based compensation 6,7</t>
+          <t>Other (expense) income total</t>
         </is>
       </c>
       <c r="D307" t="inlineStr"/>
@@ -39434,19 +39462,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="R307" s="5" t="n">
-        <v>3.904537</v>
-      </c>
-      <c r="S307" s="5" t="n">
-        <v>0.279987</v>
+      <c r="R307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="T307" s="5" t="n">
-        <v>1.933902</v>
-      </c>
-      <c r="U307" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.06848</v>
+      </c>
+      <c r="U307" s="5" t="n">
+        <v>0.05515</v>
       </c>
     </row>
     <row r="308">
@@ -39457,15 +39487,19 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Other (expense) income</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Loss on spin out of assets 3</t>
-        </is>
-      </c>
-      <c r="D308" t="inlineStr"/>
+          <t>Net loss and comprehensive loss for the year</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E308" t="inlineStr">
         <is>
           <t>-</t>
@@ -39542,12 +39576,10 @@
         </is>
       </c>
       <c r="T308" s="5" t="n">
-        <v>-1.216462</v>
-      </c>
-      <c r="U308" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-14.999903</v>
+      </c>
+      <c r="U308" s="5" t="n">
+        <v>-10.409879</v>
       </c>
     </row>
     <row r="309">
@@ -39558,19 +39590,15 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Other (expense) income</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Foreign exchange</t>
-        </is>
-      </c>
-      <c r="D309" t="inlineStr">
-        <is>
-          <t>ForeignExchangeTradingGains</t>
-        </is>
-      </c>
+          <t>Basic and diluted loss per common shares</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr"/>
       <c r="E309" t="inlineStr">
         <is>
           <t>-</t>
@@ -39636,19 +39664,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="R309" s="5" t="n">
-        <v>0.110178</v>
-      </c>
-      <c r="S309" s="5" t="n">
-        <v>-0.1767</v>
+      <c r="R309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="T309" s="5" t="n">
-        <v>0.035002</v>
-      </c>
-      <c r="U309" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.1e-07</v>
+      </c>
+      <c r="U309" s="5" t="n">
+        <v>-1.2e-07</v>
       </c>
     </row>
     <row r="310">
@@ -39659,19 +39689,15 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Weighted average number of common</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="D310" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>Weighted average number of common total</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr"/>
       <c r="E310" t="inlineStr">
         <is>
           <t>-</t>
@@ -39722,30 +39748,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O310" s="5" t="n">
-        <v>0.056245</v>
+      <c r="O310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P310" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q310" s="5" t="n">
-        <v>0.014356</v>
-      </c>
-      <c r="R310" s="5" t="n">
-        <v>0.423069</v>
-      </c>
-      <c r="S310" s="5" t="n">
-        <v>0.405406</v>
+      <c r="Q310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="T310" s="5" t="n">
-        <v>0.11298</v>
-      </c>
-      <c r="U310" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>71.33617599999999</v>
+      </c>
+      <c r="U310" s="5" t="n">
+        <v>84.264438</v>
       </c>
     </row>
     <row r="311">
@@ -39756,12 +39788,12 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Other items total</t>
+          <t>Depreciation expense 5</t>
         </is>
       </c>
       <c r="D311" t="inlineStr"/>
@@ -39815,23 +39847,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O311" s="5" t="n">
-        <v>0.03978</v>
-      </c>
-      <c r="P311" s="5" t="n">
-        <v>-0.012866</v>
+      <c r="O311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q311" s="5" t="n">
-        <v>0.132291</v>
+        <v>0.021512</v>
       </c>
       <c r="R311" s="5" t="n">
-        <v>-30.19483</v>
+        <v>0.037139</v>
       </c>
       <c r="S311" s="5" t="n">
-        <v>0.228706</v>
+        <v>0.045454</v>
       </c>
       <c r="T311" s="5" t="n">
-        <v>-1.06848</v>
+        <v>0.014898</v>
       </c>
       <c r="U311" t="inlineStr">
         <is>
@@ -39847,19 +39883,15 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss</t>
-        </is>
-      </c>
-      <c r="D312" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Exploration and evaluation costs 4</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr"/>
       <c r="E312" t="inlineStr">
         <is>
           <t>-</t>
@@ -39910,23 +39942,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O312" s="5" t="n">
-        <v>-2.54916</v>
-      </c>
-      <c r="P312" s="5" t="n">
-        <v>-1.956228</v>
+      <c r="O312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q312" s="5" t="n">
-        <v>-6.89276</v>
+        <v>4.237741</v>
       </c>
       <c r="R312" s="5" t="n">
-        <v>-53.589604</v>
+        <v>16.025598</v>
       </c>
       <c r="S312" s="5" t="n">
-        <v>-27.013835</v>
+        <v>22.405903</v>
       </c>
       <c r="T312" s="5" t="n">
-        <v>-14.999903</v>
+        <v>9.207822999999999</v>
       </c>
       <c r="U312" t="inlineStr">
         <is>
@@ -39942,17 +39978,17 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per common share</t>
+          <t>Management and director fees 7</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
@@ -40005,23 +40041,25 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O313" s="5" t="n">
-        <v>-3e-08</v>
+      <c r="O313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P313" s="5" t="n">
-        <v>-2e-08</v>
+        <v>1.387916</v>
       </c>
       <c r="Q313" s="5" t="n">
-        <v>-3e-08</v>
+        <v>0.971468</v>
       </c>
       <c r="R313" s="5" t="n">
-        <v>-1.9e-07</v>
+        <v>1.952614</v>
       </c>
       <c r="S313" s="5" t="n">
-        <v>-9e-08</v>
+        <v>3.03872</v>
       </c>
       <c r="T313" s="5" t="n">
-        <v>-4e-08</v>
+        <v>1.545587</v>
       </c>
       <c r="U313" t="inlineStr">
         <is>
@@ -40037,12 +40075,12 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding - basic and diluted</t>
+          <t>Stock based compensation 6,7</t>
         </is>
       </c>
       <c r="D314" t="inlineStr"/>
@@ -40106,17 +40144,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q314" s="5" t="n">
-        <v>237.292386</v>
+      <c r="Q314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R314" s="5" t="n">
-        <v>275.218812</v>
+        <v>3.904537</v>
       </c>
       <c r="S314" s="5" t="n">
-        <v>310.650603</v>
+        <v>0.279987</v>
       </c>
       <c r="T314" s="5" t="n">
-        <v>356.680882</v>
+        <v>1.933902</v>
       </c>
       <c r="U314" t="inlineStr">
         <is>
@@ -40132,12 +40172,12 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Depreciation expense 4</t>
+          <t>Loss on spin out of assets 3</t>
         </is>
       </c>
       <c r="D315" t="inlineStr"/>
@@ -40206,16 +40246,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="R315" s="5" t="n">
-        <v>0.037139</v>
-      </c>
-      <c r="S315" s="5" t="n">
-        <v>0.045454</v>
-      </c>
-      <c r="T315" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="R315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T315" s="5" t="n">
+        <v>-1.216462</v>
       </c>
       <c r="U315" t="inlineStr">
         <is>
@@ -40231,15 +40273,19 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Exploration and evaluation costs 3</t>
-        </is>
-      </c>
-      <c r="D316" t="inlineStr"/>
+          <t>Foreign exchange</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>ForeignExchangeTradingGains</t>
+        </is>
+      </c>
       <c r="E316" t="inlineStr">
         <is>
           <t>-</t>
@@ -40306,15 +40352,13 @@
         </is>
       </c>
       <c r="R316" s="5" t="n">
-        <v>16.025598</v>
+        <v>0.110178</v>
       </c>
       <c r="S316" s="5" t="n">
-        <v>22.405903</v>
-      </c>
-      <c r="T316" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.1767</v>
+      </c>
+      <c r="T316" s="5" t="n">
+        <v>0.035002</v>
       </c>
       <c r="U316" t="inlineStr">
         <is>
@@ -40330,15 +40374,19 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Stock based compensation 5, 6</t>
-        </is>
-      </c>
-      <c r="D317" t="inlineStr"/>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
       <c r="E317" t="inlineStr">
         <is>
           <t>-</t>
@@ -40389,31 +40437,25 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O317" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O317" s="5" t="n">
+        <v>0.056245</v>
       </c>
       <c r="P317" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q317" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q317" s="5" t="n">
+        <v>0.014356</v>
       </c>
       <c r="R317" s="5" t="n">
-        <v>3.904537</v>
+        <v>0.423069</v>
       </c>
       <c r="S317" s="5" t="n">
-        <v>0.279987</v>
-      </c>
-      <c r="T317" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.405406</v>
+      </c>
+      <c r="T317" s="5" t="n">
+        <v>0.11298</v>
       </c>
       <c r="U317" t="inlineStr">
         <is>
@@ -40434,7 +40476,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Impairment of property acquisition costs 3</t>
+          <t>Other items total</t>
         </is>
       </c>
       <c r="D318" t="inlineStr"/>
@@ -40488,33 +40530,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O318" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P318" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q318" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O318" s="5" t="n">
+        <v>0.03978</v>
+      </c>
+      <c r="P318" s="5" t="n">
+        <v>-0.012866</v>
+      </c>
+      <c r="Q318" s="5" t="n">
+        <v>0.132291</v>
       </c>
       <c r="R318" s="5" t="n">
-        <v>-30.728077</v>
-      </c>
-      <c r="S318" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T318" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-30.19483</v>
+      </c>
+      <c r="S318" s="5" t="n">
+        <v>0.228706</v>
+      </c>
+      <c r="T318" s="5" t="n">
+        <v>-1.06848</v>
       </c>
       <c r="U318" t="inlineStr">
         <is>
@@ -40535,10 +40567,14 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Impairment of property acquisition costs 4</t>
-        </is>
-      </c>
-      <c r="D319" t="inlineStr"/>
+          <t>Loss and comprehensive loss</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E319" t="inlineStr">
         <is>
           <t>-</t>
@@ -40589,33 +40625,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O319" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P319" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q319" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O319" s="5" t="n">
+        <v>-2.54916</v>
+      </c>
+      <c r="P319" s="5" t="n">
+        <v>-1.956228</v>
+      </c>
+      <c r="Q319" s="5" t="n">
+        <v>-6.89276</v>
       </c>
       <c r="R319" s="5" t="n">
-        <v>-30.728077</v>
-      </c>
-      <c r="S319" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T319" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-53.589604</v>
+      </c>
+      <c r="S319" s="5" t="n">
+        <v>-27.013835</v>
+      </c>
+      <c r="T319" s="5" t="n">
+        <v>-14.999903</v>
       </c>
       <c r="U319" t="inlineStr">
         <is>
@@ -40636,12 +40662,12 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Foreign exchange gain</t>
+          <t>Basic and diluted loss per common share</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
@@ -40694,31 +40720,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O320" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P320" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O320" s="5" t="n">
+        <v>-3e-08</v>
+      </c>
+      <c r="P320" s="5" t="n">
+        <v>-2e-08</v>
       </c>
       <c r="Q320" s="5" t="n">
-        <v>0.117935</v>
+        <v>-3e-08</v>
       </c>
       <c r="R320" s="5" t="n">
-        <v>0.110178</v>
-      </c>
-      <c r="S320" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T320" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.9e-07</v>
+      </c>
+      <c r="S320" s="5" t="n">
+        <v>-9e-08</v>
+      </c>
+      <c r="T320" s="5" t="n">
+        <v>-4e-08</v>
       </c>
       <c r="U320" t="inlineStr">
         <is>
@@ -40734,19 +40752,15 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Depreciation 5</t>
-        </is>
-      </c>
-      <c r="D321" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
+          <t>Weighted average number of common shares outstanding - basic and diluted</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr"/>
       <c r="E321" t="inlineStr">
         <is>
           <t>-</t>
@@ -40808,22 +40822,16 @@
         </is>
       </c>
       <c r="Q321" s="5" t="n">
-        <v>0.021512</v>
-      </c>
-      <c r="R321" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S321" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T321" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>237.292386</v>
+      </c>
+      <c r="R321" s="5" t="n">
+        <v>275.218812</v>
+      </c>
+      <c r="S321" s="5" t="n">
+        <v>310.650603</v>
+      </c>
+      <c r="T321" s="5" t="n">
+        <v>356.680882</v>
       </c>
       <c r="U321" t="inlineStr">
         <is>
@@ -40839,12 +40847,12 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Impairment of exploration and evaluation assets 4</t>
+          <t>Depreciation expense 4</t>
         </is>
       </c>
       <c r="D322" t="inlineStr"/>
@@ -40908,18 +40916,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q322" s="5" t="n">
-        <v>-7.16009</v>
-      </c>
-      <c r="R322" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S322" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R322" s="5" t="n">
+        <v>0.037139</v>
+      </c>
+      <c r="S322" s="5" t="n">
+        <v>0.045454</v>
       </c>
       <c r="T322" t="inlineStr">
         <is>
@@ -40940,19 +40946,15 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Foreign exchange gain (loss)</t>
-        </is>
-      </c>
-      <c r="D323" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Exploration and evaluation costs 3</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr"/>
       <c r="E323" t="inlineStr">
         <is>
           <t>-</t>
@@ -41008,21 +41010,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P323" s="5" t="n">
-        <v>-0.012866</v>
-      </c>
-      <c r="Q323" s="5" t="n">
-        <v>0.117935</v>
-      </c>
-      <c r="R323" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S323" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R323" s="5" t="n">
+        <v>16.025598</v>
+      </c>
+      <c r="S323" s="5" t="n">
+        <v>22.405903</v>
       </c>
       <c r="T323" t="inlineStr">
         <is>
@@ -41043,12 +41045,12 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding -</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding - basic and diluted</t>
+          <t>Stock based compensation 5, 6</t>
         </is>
       </c>
       <c r="D324" t="inlineStr"/>
@@ -41107,21 +41109,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P324" s="5" t="n">
-        <v>95.33228699999999</v>
-      </c>
-      <c r="Q324" s="5" t="n">
-        <v>237.292386</v>
-      </c>
-      <c r="R324" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S324" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R324" s="5" t="n">
+        <v>3.904537</v>
+      </c>
+      <c r="S324" s="5" t="n">
+        <v>0.279987</v>
       </c>
       <c r="T324" t="inlineStr">
         <is>
@@ -41142,12 +41144,12 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Advertising</t>
+          <t>Impairment of property acquisition costs 3</t>
         </is>
       </c>
       <c r="D325" t="inlineStr"/>
@@ -41201,21 +41203,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O325" s="5" t="n">
-        <v>0.0975</v>
-      </c>
-      <c r="P325" s="5" t="n">
-        <v>0.069582</v>
+      <c r="O325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q325" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R325" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="R325" s="5" t="n">
+        <v>-30.728077</v>
       </c>
       <c r="S325" t="inlineStr">
         <is>
@@ -41241,12 +41245,12 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Share-based compensation 5,6</t>
+          <t>Impairment of property acquisition costs 4</t>
         </is>
       </c>
       <c r="D326" t="inlineStr"/>
@@ -41300,8 +41304,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O326" s="5" t="n">
-        <v>0.331406</v>
+      <c r="O326" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P326" t="inlineStr">
         <is>
@@ -41313,10 +41319,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="R326" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="R326" s="5" t="n">
+        <v>-30.728077</v>
       </c>
       <c r="S326" t="inlineStr">
         <is>
@@ -41347,10 +41351,14 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Gain on disposal of exploration and evaluation assets 4</t>
-        </is>
-      </c>
-      <c r="D327" t="inlineStr"/>
+          <t>Foreign exchange gain</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E327" t="inlineStr">
         <is>
           <t>-</t>
@@ -41401,23 +41409,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O327" s="5" t="n">
-        <v>0.010407</v>
+      <c r="O327" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P327" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q327" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R327" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q327" s="5" t="n">
+        <v>0.117935</v>
+      </c>
+      <c r="R327" s="5" t="n">
+        <v>0.110178</v>
       </c>
       <c r="S327" t="inlineStr">
         <is>
@@ -41443,17 +41449,17 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Foreign exchange loss</t>
+          <t>Depreciation 5</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -41506,16 +41512,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O328" s="5" t="n">
-        <v>-0.026872</v>
-      </c>
-      <c r="P328" s="5" t="n">
-        <v>-0.012866</v>
-      </c>
-      <c r="Q328" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q328" s="5" t="n">
+        <v>0.021512</v>
       </c>
       <c r="R328" t="inlineStr">
         <is>
@@ -41551,14 +41559,10 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
-        </is>
-      </c>
-      <c r="D329" t="inlineStr">
-        <is>
-          <t>SharesOutstanding</t>
-        </is>
-      </c>
+          <t>Impairment of exploration and evaluation assets 4</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr"/>
       <c r="E329" t="inlineStr">
         <is>
           <t>-</t>
@@ -41609,16 +41613,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O329" s="5" t="n">
-        <v>90.14084099999999</v>
-      </c>
-      <c r="P329" s="5" t="n">
-        <v>95.33228699999999</v>
-      </c>
-      <c r="Q329" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q329" s="5" t="n">
+        <v>-7.16009</v>
       </c>
       <c r="R329" t="inlineStr">
         <is>
@@ -41649,15 +41655,19 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Advertising</t>
-        </is>
-      </c>
-      <c r="D330" t="inlineStr"/>
+          <t>Foreign exchange gain (loss)</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E330" t="inlineStr">
         <is>
           <t>-</t>
@@ -41703,21 +41713,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N330" s="5" t="n">
-        <v>0.033555</v>
-      </c>
-      <c r="O330" s="5" t="n">
-        <v>0.0975</v>
-      </c>
-      <c r="P330" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q330" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N330" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O330" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P330" s="5" t="n">
+        <v>-0.012866</v>
+      </c>
+      <c r="Q330" s="5" t="n">
+        <v>0.117935</v>
       </c>
       <c r="R330" t="inlineStr">
         <is>
@@ -41748,19 +41758,15 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Weighted average number of common shares outstanding -</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Consulting</t>
-        </is>
-      </c>
-      <c r="D331" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
+          <t>Weighted average number of common shares outstanding - basic and diluted</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr"/>
       <c r="E331" t="inlineStr">
         <is>
           <t>-</t>
@@ -41806,21 +41812,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N331" s="5" t="n">
-        <v>0.056</v>
-      </c>
-      <c r="O331" s="5" t="n">
-        <v>0.276</v>
-      </c>
-      <c r="P331" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q331" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N331" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O331" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P331" s="5" t="n">
+        <v>95.33228699999999</v>
+      </c>
+      <c r="Q331" s="5" t="n">
+        <v>237.292386</v>
       </c>
       <c r="R331" t="inlineStr">
         <is>
@@ -41851,12 +41857,12 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Management and directors fees 6</t>
+          <t>Advertising</t>
         </is>
       </c>
       <c r="D332" t="inlineStr"/>
@@ -41905,16 +41911,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N332" s="5" t="n">
-        <v>0.31811</v>
+      <c r="N332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O332" s="5" t="n">
-        <v>1.495855</v>
-      </c>
-      <c r="P332" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.0975</v>
+      </c>
+      <c r="P332" s="5" t="n">
+        <v>0.069582</v>
       </c>
       <c r="Q332" t="inlineStr">
         <is>
@@ -41950,12 +41956,12 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Office and sundry</t>
+          <t>Share-based compensation 5,6</t>
         </is>
       </c>
       <c r="D333" t="inlineStr"/>
@@ -42004,11 +42010,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N333" s="5" t="n">
-        <v>0.026464</v>
+      <c r="N333" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O333" s="5" t="n">
-        <v>0.166406</v>
+        <v>0.331406</v>
       </c>
       <c r="P333" t="inlineStr">
         <is>
@@ -42049,19 +42057,15 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Professional fees</t>
-        </is>
-      </c>
-      <c r="D334" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>Gain on disposal of exploration and evaluation assets 4</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr"/>
       <c r="E334" t="inlineStr">
         <is>
           <t>-</t>
@@ -42077,29 +42081,43 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H334" s="5" t="n">
-        <v>0.054302</v>
-      </c>
-      <c r="I334" s="5" t="n">
-        <v>0.020725</v>
-      </c>
-      <c r="J334" s="5" t="n">
-        <v>0.019281</v>
-      </c>
-      <c r="K334" s="5" t="n">
-        <v>0.011864</v>
-      </c>
-      <c r="L334" s="5" t="n">
-        <v>0.03997</v>
-      </c>
-      <c r="M334" s="5" t="n">
-        <v>0.015817</v>
-      </c>
-      <c r="N334" s="5" t="n">
-        <v>0.009577</v>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J334" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M334" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N334" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O334" s="5" t="n">
-        <v>0.058746</v>
+        <v>0.010407</v>
       </c>
       <c r="P334" t="inlineStr">
         <is>
@@ -42140,15 +42158,19 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Share-based compensation 5, 6</t>
-        </is>
-      </c>
-      <c r="D335" t="inlineStr"/>
+          <t>Foreign exchange loss</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E335" t="inlineStr">
         <is>
           <t>-</t>
@@ -42194,16 +42216,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N335" s="5" t="n">
-        <v>2.102198</v>
+      <c r="N335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O335" s="5" t="n">
-        <v>0.331406</v>
-      </c>
-      <c r="P335" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.026872</v>
+      </c>
+      <c r="P335" s="5" t="n">
+        <v>-0.012866</v>
       </c>
       <c r="Q335" t="inlineStr">
         <is>
@@ -42239,17 +42261,17 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Transfer agent and regulatory fees</t>
+          <t>Weighted average number of common shares outstanding</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>SharesOutstanding</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
@@ -42297,16 +42319,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N336" s="5" t="n">
-        <v>0.008669</v>
+      <c r="N336" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O336" s="5" t="n">
-        <v>0.05804</v>
-      </c>
-      <c r="P336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>90.14084099999999</v>
+      </c>
+      <c r="P336" s="5" t="n">
+        <v>95.33228699999999</v>
       </c>
       <c r="Q336" t="inlineStr">
         <is>
@@ -42347,14 +42369,10 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Travel</t>
-        </is>
-      </c>
-      <c r="D337" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Advertising</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr"/>
       <c r="E337" t="inlineStr">
         <is>
           <t>-</t>
@@ -42401,10 +42419,10 @@
         </is>
       </c>
       <c r="N337" s="5" t="n">
-        <v>0.023199</v>
+        <v>0.033555</v>
       </c>
       <c r="O337" s="5" t="n">
-        <v>0.104987</v>
+        <v>0.0975</v>
       </c>
       <c r="P337" t="inlineStr">
         <is>
@@ -42450,10 +42468,14 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Loss from operating activities</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr"/>
+          <t>Consulting</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E338" t="inlineStr">
         <is>
           <t>-</t>
@@ -42500,10 +42522,10 @@
         </is>
       </c>
       <c r="N338" s="5" t="n">
-        <v>-2.577772</v>
+        <v>0.056</v>
       </c>
       <c r="O338" s="5" t="n">
-        <v>-2.58894</v>
+        <v>0.276</v>
       </c>
       <c r="P338" t="inlineStr">
         <is>
@@ -42549,12 +42571,12 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Foreign exchange (loss) gain</t>
+          <t>Management and directors fees 6</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
@@ -42603,10 +42625,10 @@
         </is>
       </c>
       <c r="N339" s="5" t="n">
-        <v>0.007158</v>
+        <v>0.31811</v>
       </c>
       <c r="O339" s="5" t="n">
-        <v>-0.026872</v>
+        <v>1.495855</v>
       </c>
       <c r="P339" t="inlineStr">
         <is>
@@ -42652,14 +42674,10 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="D340" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>Office and sundry</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr"/>
       <c r="E340" t="inlineStr">
         <is>
           <t>-</t>
@@ -42705,13 +42723,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N340" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N340" s="5" t="n">
+        <v>0.026464</v>
       </c>
       <c r="O340" s="5" t="n">
-        <v>0.056245</v>
+        <v>0.166406</v>
       </c>
       <c r="P340" t="inlineStr">
         <is>
@@ -42757,10 +42773,14 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Listing expense 3</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr"/>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E341" t="inlineStr">
         <is>
           <t>-</t>
@@ -42776,43 +42796,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H341" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I341" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J341" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K341" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L341" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M341" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H341" s="5" t="n">
+        <v>0.054302</v>
+      </c>
+      <c r="I341" s="5" t="n">
+        <v>0.020725</v>
+      </c>
+      <c r="J341" s="5" t="n">
+        <v>0.019281</v>
+      </c>
+      <c r="K341" s="5" t="n">
+        <v>0.011864</v>
+      </c>
+      <c r="L341" s="5" t="n">
+        <v>0.03997</v>
+      </c>
+      <c r="M341" s="5" t="n">
+        <v>0.015817</v>
       </c>
       <c r="N341" s="5" t="n">
-        <v>-6.73096</v>
-      </c>
-      <c r="O341" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.009577</v>
+      </c>
+      <c r="O341" s="5" t="n">
+        <v>0.058746</v>
       </c>
       <c r="P341" t="inlineStr">
         <is>
@@ -42858,7 +42864,7 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Gain (loss) on disposal of exploration and evaluation assets 4ii</t>
+          <t>Share-based compensation 5, 6</t>
         </is>
       </c>
       <c r="D342" t="inlineStr"/>
@@ -42908,10 +42914,10 @@
         </is>
       </c>
       <c r="N342" s="5" t="n">
-        <v>-0.185632</v>
+        <v>2.102198</v>
       </c>
       <c r="O342" s="5" t="n">
-        <v>0.010407</v>
+        <v>0.331406</v>
       </c>
       <c r="P342" t="inlineStr">
         <is>
@@ -42957,12 +42963,12 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the period</t>
+          <t>Transfer agent and regulatory fees</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
@@ -43011,10 +43017,10 @@
         </is>
       </c>
       <c r="N343" s="5" t="n">
-        <v>-9.487206</v>
+        <v>0.008669</v>
       </c>
       <c r="O343" s="5" t="n">
-        <v>-2.54916</v>
+        <v>0.05804</v>
       </c>
       <c r="P343" t="inlineStr">
         <is>
@@ -43060,12 +43066,12 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Loss per share – basic and diluted ($)</t>
+          <t>Travel</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
@@ -43114,10 +43120,10 @@
         </is>
       </c>
       <c r="N344" s="5" t="n">
-        <v>-2.4e-07</v>
+        <v>0.023199</v>
       </c>
       <c r="O344" s="5" t="n">
-        <v>-3e-08</v>
+        <v>0.104987</v>
       </c>
       <c r="P344" t="inlineStr">
         <is>
@@ -43163,7 +43169,7 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding – basic and diluted</t>
+          <t>Loss from operating activities</t>
         </is>
       </c>
       <c r="D345" t="inlineStr"/>
@@ -43213,10 +43219,10 @@
         </is>
       </c>
       <c r="N345" s="5" t="n">
-        <v>40.315212</v>
+        <v>-2.577772</v>
       </c>
       <c r="O345" s="5" t="n">
-        <v>90.14084099999999</v>
+        <v>-2.58894</v>
       </c>
       <c r="P345" t="inlineStr">
         <is>
@@ -43262,12 +43268,12 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>General and administrative (Note 5) $</t>
+          <t>Foreign exchange (loss) gain</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>GeneralAndAdministrativeExpense</t>
+          <t>OtherIncomeExpense</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
@@ -43305,21 +43311,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L346" s="5" t="n">
-        <v>0.014764</v>
-      </c>
-      <c r="M346" s="5" t="n">
-        <v>0.014501</v>
-      </c>
-      <c r="N346" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O346" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L346" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M346" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N346" s="5" t="n">
+        <v>0.007158</v>
+      </c>
+      <c r="O346" s="5" t="n">
+        <v>-0.026872</v>
       </c>
       <c r="P346" t="inlineStr">
         <is>
@@ -43365,12 +43371,12 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Management fees (Note 5)</t>
+          <t>Interest income</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
@@ -43388,33 +43394,43 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H347" s="5" t="n">
-        <v>0.07199999999999999</v>
-      </c>
-      <c r="I347" s="5" t="n">
-        <v>0.108</v>
-      </c>
-      <c r="J347" s="5" t="n">
-        <v>0.108</v>
-      </c>
-      <c r="K347" s="5" t="n">
-        <v>0.108</v>
-      </c>
-      <c r="L347" s="5" t="n">
-        <v>0.07975</v>
-      </c>
-      <c r="M347" s="5" t="n">
-        <v>0.0504</v>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J347" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M347" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N347" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O347" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O347" s="5" t="n">
+        <v>0.056245</v>
       </c>
       <c r="P347" t="inlineStr">
         <is>
@@ -43460,14 +43476,10 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Transfer agent and filing fees</t>
-        </is>
-      </c>
-      <c r="D348" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Listing expense 3</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr"/>
       <c r="E348" t="inlineStr">
         <is>
           <t>-</t>
@@ -43493,22 +43505,28 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J348" s="5" t="n">
-        <v>0.009039</v>
-      </c>
-      <c r="K348" s="5" t="n">
-        <v>0.011233</v>
-      </c>
-      <c r="L348" s="5" t="n">
-        <v>0.014511</v>
-      </c>
-      <c r="M348" s="5" t="n">
-        <v>0.014156</v>
-      </c>
-      <c r="N348" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N348" s="5" t="n">
+        <v>-6.73096</v>
       </c>
       <c r="O348" t="inlineStr">
         <is>
@@ -43559,14 +43577,10 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss $</t>
-        </is>
-      </c>
-      <c r="D349" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Gain (loss) on disposal of exploration and evaluation assets 4ii</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr"/>
       <c r="E349" t="inlineStr">
         <is>
           <t>-</t>
@@ -43592,27 +43606,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J349" s="5" t="n">
-        <v>-0.15037</v>
-      </c>
-      <c r="K349" s="5" t="n">
-        <v>-0.186617</v>
-      </c>
-      <c r="L349" s="5" t="n">
-        <v>-0.148995</v>
-      </c>
-      <c r="M349" s="5" t="n">
-        <v>-0.094874</v>
-      </c>
-      <c r="N349" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O349" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M349" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N349" s="5" t="n">
+        <v>-0.185632</v>
+      </c>
+      <c r="O349" s="5" t="n">
+        <v>0.010407</v>
       </c>
       <c r="P349" t="inlineStr">
         <is>
@@ -43658,10 +43676,14 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding - basic and diluted</t>
-        </is>
-      </c>
-      <c r="D350" t="inlineStr"/>
+          <t>Loss and comprehensive loss for the period</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E350" t="inlineStr">
         <is>
           <t>-</t>
@@ -43687,27 +43709,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J350" s="5" t="n">
-        <v>13.791303</v>
-      </c>
-      <c r="K350" s="5" t="n">
-        <v>6.895651</v>
-      </c>
-      <c r="L350" s="5" t="n">
-        <v>11.813233</v>
-      </c>
-      <c r="M350" s="5" t="n">
-        <v>21.964126</v>
-      </c>
-      <c r="N350" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O350" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M350" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N350" s="5" t="n">
+        <v>-9.487206</v>
+      </c>
+      <c r="O350" s="5" t="n">
+        <v>-2.54916</v>
       </c>
       <c r="P350" t="inlineStr">
         <is>
@@ -43753,7 +43779,7 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share $</t>
+          <t>Loss per share – basic and diluted ($)</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -43786,27 +43812,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J351" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="K351" s="5" t="n">
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M351" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N351" s="5" t="n">
+        <v>-2.4e-07</v>
+      </c>
+      <c r="O351" s="5" t="n">
         <v>-3e-08</v>
-      </c>
-      <c r="L351" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="M351" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N351" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O351" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="P351" t="inlineStr">
         <is>
@@ -43847,12 +43877,12 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Shares                     Reserve                         Equity</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Balance, March 31, 2016 6,895,651 $ 8,680,337 $ 498,873 $</t>
+          <t>Weighted average number of common shares outstanding – basic and diluted</t>
         </is>
       </c>
       <c r="D352" t="inlineStr"/>
@@ -43886,24 +43916,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K352" s="5" t="n">
-        <v>0.080791</v>
-      </c>
-      <c r="L352" s="5" t="n">
-        <v>0.080791</v>
-      </c>
-      <c r="M352" s="5" t="n">
-        <v>-9.098419</v>
-      </c>
-      <c r="N352" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O352" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N352" s="5" t="n">
+        <v>40.315212</v>
+      </c>
+      <c r="O352" s="5" t="n">
+        <v>90.14084099999999</v>
       </c>
       <c r="P352" t="inlineStr">
         <is>
@@ -43944,17 +43976,17 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Shares                     Reserve                         Equity</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Loss for the year - - -</t>
+          <t>General and administrative (Note 5) $</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>GeneralAndAdministrativeExpense</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
@@ -43982,17 +44014,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J353" s="5" t="n">
-        <v>-0.15037</v>
-      </c>
-      <c r="K353" s="5" t="n">
-        <v>-0.186617</v>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L353" s="5" t="n">
-        <v>-0.148995</v>
+        <v>0.014764</v>
       </c>
       <c r="M353" s="5" t="n">
-        <v>-0.148995</v>
+        <v>0.014501</v>
       </c>
       <c r="N353" t="inlineStr">
         <is>
@@ -44043,15 +44079,19 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Shares                     Reserve                         Equity</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Share issuance 10,000,000 500,000 -</t>
-        </is>
-      </c>
-      <c r="D354" t="inlineStr"/>
+          <t>Management fees (Note 5)</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E354" t="inlineStr">
         <is>
           <t>-</t>
@@ -44067,31 +44107,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H354" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I354" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J354" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H354" s="5" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="I354" s="5" t="n">
+        <v>0.108</v>
+      </c>
+      <c r="J354" s="5" t="n">
+        <v>0.108</v>
       </c>
       <c r="K354" s="5" t="n">
-        <v>0.5</v>
+        <v>0.108</v>
       </c>
       <c r="L354" s="5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M354" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.07975</v>
+      </c>
+      <c r="M354" s="5" t="n">
+        <v>0.0504</v>
       </c>
       <c r="N354" t="inlineStr">
         <is>
@@ -44142,15 +44174,19 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Shares                     Reserve                         Equity</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Share issuance costs (10,000) -</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr"/>
+          <t>Transfer agent and filing fees</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E355" t="inlineStr">
         <is>
           <t>-</t>
@@ -44176,21 +44212,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J355" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J355" s="5" t="n">
+        <v>0.009039</v>
       </c>
       <c r="K355" s="5" t="n">
-        <v>-0.01</v>
+        <v>0.011233</v>
       </c>
       <c r="L355" s="5" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="M355" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.014511</v>
+      </c>
+      <c r="M355" s="5" t="n">
+        <v>0.014156</v>
       </c>
       <c r="N355" t="inlineStr">
         <is>
@@ -44241,15 +44273,19 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Shares                     Reserve                         Equity</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Balance, March 31, 2017 16,895,651 $ 9,170,337 $ 498,873 $</t>
-        </is>
-      </c>
-      <c r="D356" t="inlineStr"/>
+          <t>Loss and comprehensive loss $</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E356" t="inlineStr">
         <is>
           <t>-</t>
@@ -44275,19 +44311,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J356" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J356" s="5" t="n">
+        <v>-0.15037</v>
       </c>
       <c r="K356" s="5" t="n">
-        <v>0.421796</v>
+        <v>-0.186617</v>
       </c>
       <c r="L356" s="5" t="n">
-        <v>0.421796</v>
+        <v>-0.148995</v>
       </c>
       <c r="M356" s="5" t="n">
-        <v>-9.247413999999999</v>
+        <v>-0.094874</v>
       </c>
       <c r="N356" t="inlineStr">
         <is>
@@ -44338,12 +44372,12 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Shares                     Reserve                         Equity</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Warrants exercised 10,000,000 600,000 -</t>
+          <t>Weighted average number of shares outstanding - basic and diluted</t>
         </is>
       </c>
       <c r="D357" t="inlineStr"/>
@@ -44372,23 +44406,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J357" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K357" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J357" s="5" t="n">
+        <v>13.791303</v>
+      </c>
+      <c r="K357" s="5" t="n">
+        <v>6.895651</v>
       </c>
       <c r="L357" s="5" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="M357" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>11.813233</v>
+      </c>
+      <c r="M357" s="5" t="n">
+        <v>21.964126</v>
       </c>
       <c r="N357" t="inlineStr">
         <is>
@@ -44439,15 +44467,19 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Shares                     Reserve                         Equity</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Balance, March 31, 2018 26,895,651 $ 9,770,337 $ 498,873 $</t>
-        </is>
-      </c>
-      <c r="D358" t="inlineStr"/>
+          <t>Basic and diluted loss per share $</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E358" t="inlineStr">
         <is>
           <t>-</t>
@@ -44473,21 +44505,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J358" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K358" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J358" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="K358" s="5" t="n">
+        <v>-3e-08</v>
       </c>
       <c r="L358" s="5" t="n">
-        <v>0.926922</v>
+        <v>-1e-08</v>
       </c>
       <c r="M358" s="5" t="n">
-        <v>-9.342288</v>
+        <v>0</v>
       </c>
       <c r="N358" t="inlineStr">
         <is>
@@ -44538,19 +44566,15 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Shares                     Reserve                         Equity</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Consulting fees $</t>
-        </is>
-      </c>
-      <c r="D359" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Balance, March 31, 2016 6,895,651 $ 8,680,337 $ 498,873 $</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr"/>
       <c r="E359" t="inlineStr">
         <is>
           <t>-</t>
@@ -44582,17 +44606,13 @@
         </is>
       </c>
       <c r="K359" s="5" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="L359" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M359" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.080791</v>
+      </c>
+      <c r="L359" s="5" t="n">
+        <v>0.080791</v>
+      </c>
+      <c r="M359" s="5" t="n">
+        <v>-9.098419</v>
       </c>
       <c r="N359" t="inlineStr">
         <is>
@@ -44643,17 +44663,17 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Shares                     Reserve                         Equity</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>General and administrative</t>
+          <t>Loss for the year - - -</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>GeneralAndAdministrativeExpense</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
@@ -44682,18 +44702,16 @@
         </is>
       </c>
       <c r="J360" s="5" t="n">
-        <v>0.01405</v>
+        <v>-0.15037</v>
       </c>
       <c r="K360" s="5" t="n">
-        <v>0.01512</v>
+        <v>-0.186617</v>
       </c>
       <c r="L360" s="5" t="n">
-        <v>0.014764</v>
-      </c>
-      <c r="M360" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.148995</v>
+      </c>
+      <c r="M360" s="5" t="n">
+        <v>-0.148995</v>
       </c>
       <c r="N360" t="inlineStr">
         <is>
@@ -44744,12 +44762,12 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Shares                     Reserve                         Equity</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Share-based compensation (Note 6)</t>
+          <t>Share issuance 10,000,000 500,000 -</t>
         </is>
       </c>
       <c r="D361" t="inlineStr"/>
@@ -44784,12 +44802,10 @@
         </is>
       </c>
       <c r="K361" s="5" t="n">
-        <v>0.0394</v>
-      </c>
-      <c r="L361" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.5</v>
+      </c>
+      <c r="L361" s="5" t="n">
+        <v>0.5</v>
       </c>
       <c r="M361" t="inlineStr">
         <is>
@@ -44850,7 +44866,7 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Balance, March 31, 2015 6,895,651 8,680,337 459,473</t>
+          <t>Share issuance costs (10,000) -</t>
         </is>
       </c>
       <c r="D362" t="inlineStr"/>
@@ -44885,10 +44901,10 @@
         </is>
       </c>
       <c r="K362" s="5" t="n">
-        <v>0.228008</v>
+        <v>-0.01</v>
       </c>
       <c r="L362" s="5" t="n">
-        <v>-8.911802</v>
+        <v>-0.01</v>
       </c>
       <c r="M362" t="inlineStr">
         <is>
@@ -44949,7 +44965,7 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Share-based payments - - 39,400</t>
+          <t>Balance, March 31, 2017 16,895,651 $ 9,170,337 $ 498,873 $</t>
         </is>
       </c>
       <c r="D363" t="inlineStr"/>
@@ -44978,21 +44994,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J363" s="5" t="n">
-        <v>0.0394</v>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K363" s="5" t="n">
-        <v>0.0394</v>
-      </c>
-      <c r="L363" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M363" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.421796</v>
+      </c>
+      <c r="L363" s="5" t="n">
+        <v>0.421796</v>
+      </c>
+      <c r="M363" s="5" t="n">
+        <v>-9.247413999999999</v>
       </c>
       <c r="N363" t="inlineStr">
         <is>
@@ -45048,7 +45062,7 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Balance, March 31, 2014 13,791,303 $ 8,680,337 $ 459,473 $</t>
+          <t>Warrants exercised 10,000,000 600,000 -</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
@@ -45077,16 +45091,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J364" s="5" t="n">
-        <v>0.378378</v>
-      </c>
-      <c r="K364" s="5" t="n">
-        <v>-8.761431999999999</v>
-      </c>
-      <c r="L364" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L364" s="5" t="n">
+        <v>0.6</v>
       </c>
       <c r="M364" t="inlineStr">
         <is>
@@ -45147,7 +45163,7 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Balance, March 31, 2015 13,791,303 8,680,337 459,473</t>
+          <t>Balance, March 31, 2018 26,895,651 $ 9,770,337 $ 498,873 $</t>
         </is>
       </c>
       <c r="D365" t="inlineStr"/>
@@ -45176,21 +45192,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J365" s="5" t="n">
-        <v>0.228008</v>
-      </c>
-      <c r="K365" s="5" t="n">
-        <v>-8.911802</v>
-      </c>
-      <c r="L365" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M365" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J365" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L365" s="5" t="n">
+        <v>0.926922</v>
+      </c>
+      <c r="M365" s="5" t="n">
+        <v>-9.342288</v>
       </c>
       <c r="N365" t="inlineStr">
         <is>
@@ -45241,15 +45257,19 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Shares                     Reserve                         Equity</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Balance, March 31, 2016 13,791,303 $ 8,680,337 $ 498,873 $</t>
-        </is>
-      </c>
-      <c r="D366" t="inlineStr"/>
+          <t>Consulting fees $</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E366" t="inlineStr">
         <is>
           <t>-</t>
@@ -45275,11 +45295,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J366" s="5" t="n">
-        <v>0.080791</v>
+      <c r="J366" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K366" s="5" t="n">
-        <v>-9.098419</v>
+        <v>0.001</v>
       </c>
       <c r="L366" t="inlineStr">
         <is>
@@ -45340,15 +45362,19 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Current Assets</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Cash $</t>
-        </is>
-      </c>
-      <c r="D367" t="inlineStr"/>
+          <t>General and administrative</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E367" t="inlineStr">
         <is>
           <t>-</t>
@@ -45369,21 +45395,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I367" s="5" t="n">
-        <v>0.390062</v>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J367" s="5" t="n">
-        <v>0.237503</v>
-      </c>
-      <c r="K367" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L367" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.01405</v>
+      </c>
+      <c r="K367" s="5" t="n">
+        <v>0.01512</v>
+      </c>
+      <c r="L367" s="5" t="n">
+        <v>0.014764</v>
       </c>
       <c r="M367" t="inlineStr">
         <is>
@@ -45439,12 +45463,12 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Current Assets</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Receivables</t>
+          <t>Share-based compensation (Note 6)</t>
         </is>
       </c>
       <c r="D368" t="inlineStr"/>
@@ -45468,16 +45492,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I368" s="5" t="n">
-        <v>0.004682</v>
-      </c>
-      <c r="J368" s="5" t="n">
-        <v>0.001895</v>
-      </c>
-      <c r="K368" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J368" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K368" s="5" t="n">
+        <v>0.0394</v>
       </c>
       <c r="L368" t="inlineStr">
         <is>
@@ -45538,12 +45564,12 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Current Assets</t>
+          <t>Shares                     Reserve                         Equity</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Total Assets $</t>
+          <t>Balance, March 31, 2015 6,895,651 8,680,337 459,473</t>
         </is>
       </c>
       <c r="D369" t="inlineStr"/>
@@ -45567,21 +45593,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I369" s="5" t="n">
-        <v>0.394744</v>
-      </c>
-      <c r="J369" s="5" t="n">
-        <v>0.239398</v>
-      </c>
-      <c r="K369" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L369" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J369" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K369" s="5" t="n">
+        <v>0.228008</v>
+      </c>
+      <c r="L369" s="5" t="n">
+        <v>-8.911802</v>
       </c>
       <c r="M369" t="inlineStr">
         <is>
@@ -45637,12 +45663,12 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Current Liabilities</t>
+          <t>Shares                     Reserve                         Equity</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities $</t>
+          <t>Share-based payments - - 39,400</t>
         </is>
       </c>
       <c r="D370" t="inlineStr"/>
@@ -45666,16 +45692,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I370" s="5" t="n">
-        <v>0.016366</v>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J370" s="5" t="n">
-        <v>0.01139</v>
-      </c>
-      <c r="K370" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.0394</v>
+      </c>
+      <c r="K370" s="5" t="n">
+        <v>0.0394</v>
       </c>
       <c r="L370" t="inlineStr">
         <is>
@@ -45736,12 +45762,12 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Shareholders’ Equity</t>
+          <t>Shares                     Reserve                         Equity</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Share capital (Note 6)</t>
+          <t>Balance, March 31, 2014 13,791,303 $ 8,680,337 $ 459,473 $</t>
         </is>
       </c>
       <c r="D371" t="inlineStr"/>
@@ -45765,16 +45791,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I371" s="5" t="n">
-        <v>8.680337</v>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J371" s="5" t="n">
-        <v>8.680337</v>
-      </c>
-      <c r="K371" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.378378</v>
+      </c>
+      <c r="K371" s="5" t="n">
+        <v>-8.761431999999999</v>
       </c>
       <c r="L371" t="inlineStr">
         <is>
@@ -45835,12 +45861,12 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Shareholders’ Equity</t>
+          <t>Shares                     Reserve                         Equity</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Share‐based payment reserve (Note 6)</t>
+          <t>Balance, March 31, 2015 13,791,303 8,680,337 459,473</t>
         </is>
       </c>
       <c r="D372" t="inlineStr"/>
@@ -45864,16 +45890,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I372" s="5" t="n">
-        <v>0.459473</v>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J372" s="5" t="n">
-        <v>0.459473</v>
-      </c>
-      <c r="K372" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.228008</v>
+      </c>
+      <c r="K372" s="5" t="n">
+        <v>-8.911802</v>
       </c>
       <c r="L372" t="inlineStr">
         <is>
@@ -45934,12 +45960,12 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Shareholders’ Equity</t>
+          <t>Shares                     Reserve                         Equity</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Deficit</t>
+          <t>Balance, March 31, 2016 13,791,303 $ 8,680,337 $ 498,873 $</t>
         </is>
       </c>
       <c r="D373" t="inlineStr"/>
@@ -45963,16 +45989,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I373" s="5" t="n">
-        <v>-8.761431999999999</v>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J373" s="5" t="n">
-        <v>-8.911802</v>
-      </c>
-      <c r="K373" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.080791</v>
+      </c>
+      <c r="K373" s="5" t="n">
+        <v>-9.098419</v>
       </c>
       <c r="L373" t="inlineStr">
         <is>
@@ -46033,12 +46059,12 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Shareholders’ Equity</t>
+          <t>Current Assets</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Shareholders’ Equity total</t>
+          <t>Cash $</t>
         </is>
       </c>
       <c r="D374" t="inlineStr"/>
@@ -46063,10 +46089,10 @@
         </is>
       </c>
       <c r="I374" s="5" t="n">
-        <v>0.378378</v>
+        <v>0.390062</v>
       </c>
       <c r="J374" s="5" t="n">
-        <v>0.228008</v>
+        <v>0.237503</v>
       </c>
       <c r="K374" t="inlineStr">
         <is>
@@ -46132,12 +46158,12 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Shareholders’ Equity</t>
+          <t>Current Assets</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Total Liabilities and Shareholders’ Equity $</t>
+          <t>Receivables</t>
         </is>
       </c>
       <c r="D375" t="inlineStr"/>
@@ -46162,10 +46188,10 @@
         </is>
       </c>
       <c r="I375" s="5" t="n">
-        <v>0.394744</v>
+        <v>0.004682</v>
       </c>
       <c r="J375" s="5" t="n">
-        <v>0.239398</v>
+        <v>0.001895</v>
       </c>
       <c r="K375" t="inlineStr">
         <is>
@@ -46231,19 +46257,15 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Current Assets</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>General and administrative $</t>
-        </is>
-      </c>
-      <c r="D376" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Total Assets $</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr"/>
       <c r="E376" t="inlineStr">
         <is>
           <t>-</t>
@@ -46259,14 +46281,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H376" s="5" t="n">
-        <v>0.047534</v>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I376" s="5" t="n">
-        <v>0.015435</v>
+        <v>0.394744</v>
       </c>
       <c r="J376" s="5" t="n">
-        <v>0.01405</v>
+        <v>0.239398</v>
       </c>
       <c r="K376" t="inlineStr">
         <is>
@@ -46332,19 +46356,15 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Other income                                                                                          ‐          (11,037)</t>
+          <t>Current Liabilities</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Transfer agent and filing fees</t>
-        </is>
-      </c>
-      <c r="D377" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Accounts payable and accrued liabilities $</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr"/>
       <c r="E377" t="inlineStr">
         <is>
           <t>-</t>
@@ -46366,10 +46386,10 @@
         </is>
       </c>
       <c r="I377" s="5" t="n">
-        <v>0.011387</v>
+        <v>0.016366</v>
       </c>
       <c r="J377" s="5" t="n">
-        <v>0.009039</v>
+        <v>0.01139</v>
       </c>
       <c r="K377" t="inlineStr">
         <is>
@@ -46435,19 +46455,15 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Other income                                                                                          ‐          (11,037)</t>
+          <t>Shareholders’ Equity</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss $</t>
-        </is>
-      </c>
-      <c r="D378" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Share capital (Note 6)</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr"/>
       <c r="E378" t="inlineStr">
         <is>
           <t>-</t>
@@ -46469,10 +46485,10 @@
         </is>
       </c>
       <c r="I378" s="5" t="n">
-        <v>-0.14451</v>
+        <v>8.680337</v>
       </c>
       <c r="J378" s="5" t="n">
-        <v>-0.15037</v>
+        <v>8.680337</v>
       </c>
       <c r="K378" t="inlineStr">
         <is>
@@ -46538,12 +46554,12 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Other income                                                                                          ‐          (11,037)</t>
+          <t>Shareholders’ Equity</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding ‐ basic and diluted</t>
+          <t>Share‐based payment reserve (Note 6)</t>
         </is>
       </c>
       <c r="D379" t="inlineStr"/>
@@ -46568,10 +46584,10 @@
         </is>
       </c>
       <c r="I379" s="5" t="n">
-        <v>13.599755</v>
+        <v>0.459473</v>
       </c>
       <c r="J379" s="5" t="n">
-        <v>13.791303</v>
+        <v>0.459473</v>
       </c>
       <c r="K379" t="inlineStr">
         <is>
@@ -46637,19 +46653,15 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Other income                                                                                          ‐          (11,037)</t>
+          <t>Shareholders’ Equity</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share $</t>
-        </is>
-      </c>
-      <c r="D380" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Deficit</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr"/>
       <c r="E380" t="inlineStr">
         <is>
           <t>-</t>
@@ -46671,10 +46683,10 @@
         </is>
       </c>
       <c r="I380" s="5" t="n">
-        <v>-2e-08</v>
+        <v>-8.761431999999999</v>
       </c>
       <c r="J380" s="5" t="n">
-        <v>-1e-08</v>
+        <v>-8.911802</v>
       </c>
       <c r="K380" t="inlineStr">
         <is>
@@ -46740,12 +46752,12 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Shares                     Reserve                         Equity</t>
+          <t>Shareholders’ Equity</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Balance, March 31, 2013 12,606,303 $ 8,561,837 $ 459,473 $</t>
+          <t>Shareholders’ Equity total</t>
         </is>
       </c>
       <c r="D381" t="inlineStr"/>
@@ -46770,10 +46782,10 @@
         </is>
       </c>
       <c r="I381" s="5" t="n">
-        <v>0.404388</v>
+        <v>0.378378</v>
       </c>
       <c r="J381" s="5" t="n">
-        <v>-8.616922000000001</v>
+        <v>0.228008</v>
       </c>
       <c r="K381" t="inlineStr">
         <is>
@@ -46839,19 +46851,15 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Warrant exercised                1,185,000       118,500                    ‐                      ‐        118,500</t>
+          <t>Shareholders’ Equity</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Loss for the year ‐ ‐ ‐</t>
-        </is>
-      </c>
-      <c r="D382" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Total Liabilities and Shareholders’ Equity $</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr"/>
       <c r="E382" t="inlineStr">
         <is>
           <t>-</t>
@@ -46873,10 +46881,10 @@
         </is>
       </c>
       <c r="I382" s="5" t="n">
-        <v>-0.14451</v>
+        <v>0.394744</v>
       </c>
       <c r="J382" s="5" t="n">
-        <v>-0.14451</v>
+        <v>0.239398</v>
       </c>
       <c r="K382" t="inlineStr">
         <is>
@@ -46942,15 +46950,19 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Warrant exercised                1,185,000       118,500                    ‐                      ‐        118,500</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Balance, March 31, 2014 13,791,303 8,680,337 459,473</t>
-        </is>
-      </c>
-      <c r="D383" t="inlineStr"/>
+          <t>General and administrative $</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E383" t="inlineStr">
         <is>
           <t>-</t>
@@ -46966,16 +46978,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H383" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H383" s="5" t="n">
+        <v>0.047534</v>
       </c>
       <c r="I383" s="5" t="n">
-        <v>0.378378</v>
+        <v>0.015435</v>
       </c>
       <c r="J383" s="5" t="n">
-        <v>-8.761431999999999</v>
+        <v>0.01405</v>
       </c>
       <c r="K383" t="inlineStr">
         <is>
@@ -47041,15 +47051,19 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Warrant exercised                1,185,000       118,500                    ‐                      ‐        118,500</t>
+          <t>Other income                                                                                          ‐          (11,037)</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Balance, March 31, 2015 13,791,303 $ 8,680,337 $ 459,473 $</t>
-        </is>
-      </c>
-      <c r="D384" t="inlineStr"/>
+          <t>Transfer agent and filing fees</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E384" t="inlineStr">
         <is>
           <t>-</t>
@@ -47071,10 +47085,10 @@
         </is>
       </c>
       <c r="I384" s="5" t="n">
-        <v>0.228008</v>
+        <v>0.011387</v>
       </c>
       <c r="J384" s="5" t="n">
-        <v>-8.911802</v>
+        <v>0.009039</v>
       </c>
       <c r="K384" t="inlineStr">
         <is>
@@ -47140,17 +47154,17 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Share‐based payments                                                                  ‐           76,300</t>
+          <t>Other income                                                                                          ‐          (11,037)</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Transfer agent and filing fees</t>
+          <t>Loss and comprehensive loss $</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
@@ -47168,16 +47182,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H385" s="5" t="n">
-        <v>0.009371000000000001</v>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I385" s="5" t="n">
-        <v>0.011387</v>
-      </c>
-      <c r="J385" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.14451</v>
+      </c>
+      <c r="J385" s="5" t="n">
+        <v>-0.15037</v>
       </c>
       <c r="K385" t="inlineStr">
         <is>
@@ -47243,12 +47257,12 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Share‐based payments                                                                  ‐           76,300</t>
+          <t>Other income                                                                                          ‐          (11,037)</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Share‐based payments                                                                  ‐           76,300 total</t>
+          <t>Weighted average number of shares outstanding ‐ basic and diluted</t>
         </is>
       </c>
       <c r="D386" t="inlineStr"/>
@@ -47267,16 +47281,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H386" s="5" t="n">
-        <v>-0.259507</v>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I386" s="5" t="n">
-        <v>-0.155547</v>
-      </c>
-      <c r="J386" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>13.599755</v>
+      </c>
+      <c r="J386" s="5" t="n">
+        <v>13.791303</v>
       </c>
       <c r="K386" t="inlineStr">
         <is>
@@ -47342,17 +47356,17 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Share‐based payments                                                                  ‐           76,300</t>
+          <t>Other income                                                                                          ‐          (11,037)</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>Basic and diluted loss per share $</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
@@ -47370,16 +47384,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H387" s="5" t="n">
-        <v>0.000885</v>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I387" s="5" t="n">
-        <v>0.011037</v>
-      </c>
-      <c r="J387" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2e-08</v>
+      </c>
+      <c r="J387" s="5" t="n">
+        <v>-1e-08</v>
       </c>
       <c r="K387" t="inlineStr">
         <is>
@@ -47445,19 +47459,15 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Share‐based payments                                                                  ‐           76,300</t>
+          <t>Shares                     Reserve                         Equity</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss $</t>
-        </is>
-      </c>
-      <c r="D388" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Balance, March 31, 2013 12,606,303 $ 8,561,837 $ 459,473 $</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr"/>
       <c r="E388" t="inlineStr">
         <is>
           <t>-</t>
@@ -47473,16 +47483,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H388" s="5" t="n">
-        <v>-0.258622</v>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I388" s="5" t="n">
-        <v>-0.14451</v>
-      </c>
-      <c r="J388" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.404388</v>
+      </c>
+      <c r="J388" s="5" t="n">
+        <v>-8.616922000000001</v>
       </c>
       <c r="K388" t="inlineStr">
         <is>
@@ -47548,15 +47558,19 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Share‐based payments                                                                  ‐           76,300</t>
+          <t>Warrant exercised                1,185,000       118,500                    ‐                      ‐        118,500</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding ‐ basic and diluted</t>
-        </is>
-      </c>
-      <c r="D389" t="inlineStr"/>
+          <t>Loss for the year ‐ ‐ ‐</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E389" t="inlineStr">
         <is>
           <t>-</t>
@@ -47572,16 +47586,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H389" s="5" t="n">
-        <v>10.989865</v>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I389" s="5" t="n">
-        <v>13.599755</v>
-      </c>
-      <c r="J389" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.14451</v>
+      </c>
+      <c r="J389" s="5" t="n">
+        <v>-0.14451</v>
       </c>
       <c r="K389" t="inlineStr">
         <is>
@@ -47647,19 +47661,15 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Share‐based payments                                                                  ‐           76,300</t>
+          <t>Warrant exercised                1,185,000       118,500                    ‐                      ‐        118,500</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share $</t>
-        </is>
-      </c>
-      <c r="D390" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Balance, March 31, 2014 13,791,303 8,680,337 459,473</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr"/>
       <c r="E390" t="inlineStr">
         <is>
           <t>-</t>
@@ -47675,16 +47685,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H390" s="5" t="n">
-        <v>-2e-08</v>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I390" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="J390" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.378378</v>
+      </c>
+      <c r="J390" s="5" t="n">
+        <v>-8.761431999999999</v>
       </c>
       <c r="K390" t="inlineStr">
         <is>
@@ -47750,12 +47760,12 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Shares                     Reserve                         Equity</t>
+          <t>Warrant exercised                1,185,000       118,500                    ‐                      ‐        118,500</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Balance, March 31, 2012 2,606,303 $ 7,980,827 $ 383,173 $</t>
+          <t>Balance, March 31, 2015 13,791,303 $ 8,680,337 $ 459,473 $</t>
         </is>
       </c>
       <c r="D391" t="inlineStr"/>
@@ -47774,16 +47784,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H391" s="5" t="n">
-        <v>0.0057</v>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I391" s="5" t="n">
-        <v>-8.3583</v>
-      </c>
-      <c r="J391" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.228008</v>
+      </c>
+      <c r="J391" s="5" t="n">
+        <v>-8.911802</v>
       </c>
       <c r="K391" t="inlineStr">
         <is>
@@ -47849,17 +47859,17 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Share‐based payments                             ‐                    ‐        76,300                      ‐         76,300</t>
+          <t>Share‐based payments                                                                  ‐           76,300</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss ‐ ‐ ‐</t>
+          <t>Transfer agent and filing fees</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
@@ -47878,10 +47888,10 @@
         </is>
       </c>
       <c r="H392" s="5" t="n">
-        <v>-0.258622</v>
+        <v>0.009371000000000001</v>
       </c>
       <c r="I392" s="5" t="n">
-        <v>-0.258622</v>
+        <v>0.011387</v>
       </c>
       <c r="J392" t="inlineStr">
         <is>
@@ -47952,12 +47962,12 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Share‐based payments                             ‐                    ‐        76,300                      ‐         76,300</t>
+          <t>Share‐based payments                                                                  ‐           76,300</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Balance, March 31, 2013 12,606,303 8,561,837 459,473</t>
+          <t>Share‐based payments                                                                  ‐           76,300 total</t>
         </is>
       </c>
       <c r="D393" t="inlineStr"/>
@@ -47977,10 +47987,10 @@
         </is>
       </c>
       <c r="H393" s="5" t="n">
-        <v>0.404388</v>
+        <v>-0.259507</v>
       </c>
       <c r="I393" s="5" t="n">
-        <v>-8.616922000000001</v>
+        <v>-0.155547</v>
       </c>
       <c r="J393" t="inlineStr">
         <is>
@@ -48051,17 +48061,17 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Warrants exercised               1,185,000       118,500                    ‐                      ‐        118,500</t>
+          <t>Share‐based payments                                                                  ‐           76,300</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss ‐ ‐ ‐</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>OtherIncomeExpense</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
@@ -48080,10 +48090,10 @@
         </is>
       </c>
       <c r="H394" s="5" t="n">
-        <v>-0.14451</v>
+        <v>0.000885</v>
       </c>
       <c r="I394" s="5" t="n">
-        <v>-0.14451</v>
+        <v>0.011037</v>
       </c>
       <c r="J394" t="inlineStr">
         <is>
@@ -48154,15 +48164,19 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Warrants exercised               1,185,000       118,500                    ‐                      ‐        118,500</t>
+          <t>Share‐based payments                                                                  ‐           76,300</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Balance, March 31, 2014 13,791,303 $ 8,680,337 $ 459,473 $</t>
-        </is>
-      </c>
-      <c r="D395" t="inlineStr"/>
+          <t>Loss and comprehensive loss $</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E395" t="inlineStr">
         <is>
           <t>-</t>
@@ -48179,10 +48193,10 @@
         </is>
       </c>
       <c r="H395" s="5" t="n">
-        <v>0.378378</v>
+        <v>-0.258622</v>
       </c>
       <c r="I395" s="5" t="n">
-        <v>-8.761431999999999</v>
+        <v>-0.14451</v>
       </c>
       <c r="J395" t="inlineStr">
         <is>
@@ -48253,19 +48267,15 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Share‐based payments                                                                  ‐           76,300</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Interest income $</t>
-        </is>
-      </c>
-      <c r="D396" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>Weighted average number of shares outstanding ‐ basic and diluted</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr"/>
       <c r="E396" t="inlineStr">
         <is>
           <t>-</t>
@@ -48276,16 +48286,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G396" s="5" t="n">
-        <v>0.01828</v>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H396" s="5" t="n">
-        <v>0.000885</v>
-      </c>
-      <c r="I396" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>10.989865</v>
+      </c>
+      <c r="I396" s="5" t="n">
+        <v>13.599755</v>
       </c>
       <c r="J396" t="inlineStr">
         <is>
@@ -48356,17 +48366,17 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Depreciation                                                                                           ‐           10,732</t>
+          <t>Share‐based payments                                                                  ‐           76,300</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>General and administrative</t>
+          <t>Basic and diluted loss per share $</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>GeneralAndAdministrativeExpense</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
@@ -48379,16 +48389,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G397" s="5" t="n">
-        <v>0.162756</v>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H397" s="5" t="n">
-        <v>0.047534</v>
-      </c>
-      <c r="I397" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2e-08</v>
+      </c>
+      <c r="I397" s="5" t="n">
+        <v>-1e-08</v>
       </c>
       <c r="J397" t="inlineStr">
         <is>
@@ -48459,19 +48469,15 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Management fees                                                  72,000                        ‐</t>
+          <t>Shares                     Reserve                         Equity</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Professional fees</t>
-        </is>
-      </c>
-      <c r="D398" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>Balance, March 31, 2012 2,606,303 $ 7,980,827 $ 383,173 $</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr"/>
       <c r="E398" t="inlineStr">
         <is>
           <t>-</t>
@@ -48482,16 +48488,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G398" s="5" t="n">
-        <v>0.033766</v>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H398" s="5" t="n">
-        <v>0.054302</v>
-      </c>
-      <c r="I398" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.0057</v>
+      </c>
+      <c r="I398" s="5" t="n">
+        <v>-8.3583</v>
       </c>
       <c r="J398" t="inlineStr">
         <is>
@@ -48562,17 +48568,17 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Share‐based compensation                                          76,300                        ‐</t>
+          <t>Share‐based payments                             ‐                    ‐        76,300                      ‐         76,300</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Transfer agent and filing fees</t>
+          <t>Loss and comprehensive loss ‐ ‐ ‐</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
@@ -48585,16 +48591,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G399" s="5" t="n">
-        <v>0.005619</v>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H399" s="5" t="n">
-        <v>0.009371000000000001</v>
-      </c>
-      <c r="I399" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.258622</v>
+      </c>
+      <c r="I399" s="5" t="n">
+        <v>-0.258622</v>
       </c>
       <c r="J399" t="inlineStr">
         <is>
@@ -48665,12 +48671,12 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Share‐based compensation                                          76,300                        ‐</t>
+          <t>Share‐based payments                             ‐                    ‐        76,300                      ‐         76,300</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Share‐based compensation                                          76,300                        ‐ total</t>
+          <t>Balance, March 31, 2013 12,606,303 8,561,837 459,473</t>
         </is>
       </c>
       <c r="D400" t="inlineStr"/>
@@ -48684,16 +48690,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G400" s="5" t="n">
-        <v>0.212873</v>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H400" s="5" t="n">
-        <v>0.259507</v>
-      </c>
-      <c r="I400" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.404388</v>
+      </c>
+      <c r="I400" s="5" t="n">
+        <v>-8.616922000000001</v>
       </c>
       <c r="J400" t="inlineStr">
         <is>
@@ -48764,17 +48770,17 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Share‐based compensation                                          76,300                        ‐</t>
+          <t>Warrants exercised               1,185,000       118,500                    ‐                      ‐        118,500</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Loss before income taxes</t>
+          <t>Loss and comprehensive loss ‐ ‐ ‐</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>PretaxIncome</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
@@ -48787,16 +48793,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G401" s="5" t="n">
-        <v>-0.194593</v>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H401" s="5" t="n">
-        <v>-0.258622</v>
-      </c>
-      <c r="I401" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.14451</v>
+      </c>
+      <c r="I401" s="5" t="n">
+        <v>-0.14451</v>
       </c>
       <c r="J401" t="inlineStr">
         <is>
@@ -48867,12 +48873,12 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Tax recovery                                                                                           ‐           54,747</t>
+          <t>Warrants exercised               1,185,000       118,500                    ‐                      ‐        118,500</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Net loss from continuing operations</t>
+          <t>Balance, March 31, 2014 13,791,303 $ 8,680,337 $ 459,473 $</t>
         </is>
       </c>
       <c r="D402" t="inlineStr"/>
@@ -48886,16 +48892,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G402" s="5" t="n">
-        <v>-0.139846</v>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H402" s="5" t="n">
-        <v>-0.258622</v>
-      </c>
-      <c r="I402" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.378378</v>
+      </c>
+      <c r="I402" s="5" t="n">
+        <v>-8.761431999999999</v>
       </c>
       <c r="J402" t="inlineStr">
         <is>
@@ -48966,17 +48972,17 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Income from discontinued operations                                                   ‐           47,375</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss $</t>
+          <t>Interest income $</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
@@ -48990,10 +48996,10 @@
         </is>
       </c>
       <c r="G403" s="5" t="n">
-        <v>-0.092471</v>
+        <v>0.01828</v>
       </c>
       <c r="H403" s="5" t="n">
-        <v>-0.258622</v>
+        <v>0.000885</v>
       </c>
       <c r="I403" t="inlineStr">
         <is>
@@ -49069,17 +49075,17 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Income from discontinued operations                                                   ‐           47,375</t>
+          <t>Depreciation                                                                                           ‐           10,732</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding</t>
+          <t>General and administrative</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>BasicAverageShares</t>
+          <t>GeneralAndAdministrativeExpense</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
@@ -49093,10 +49099,10 @@
         </is>
       </c>
       <c r="G404" s="5" t="n">
-        <v>2.606303</v>
+        <v>0.162756</v>
       </c>
       <c r="H404" s="5" t="n">
-        <v>10.989865</v>
+        <v>0.047534</v>
       </c>
       <c r="I404" t="inlineStr">
         <is>
@@ -49172,15 +49178,19 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Income from discontinued operations                                                   ‐           47,375</t>
+          <t>Management fees                                                  72,000                        ‐</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share, continuing operations $</t>
-        </is>
-      </c>
-      <c r="D405" t="inlineStr"/>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E405" t="inlineStr">
         <is>
           <t>-</t>
@@ -49192,10 +49202,10 @@
         </is>
       </c>
       <c r="G405" s="5" t="n">
-        <v>-5e-08</v>
+        <v>0.033766</v>
       </c>
       <c r="H405" s="5" t="n">
-        <v>-2e-08</v>
+        <v>0.054302</v>
       </c>
       <c r="I405" t="inlineStr">
         <is>
@@ -49271,15 +49281,19 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Income from discontinued operations                                                   ‐           47,375</t>
+          <t>Share‐based compensation                                          76,300                        ‐</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share, discontinued operations $</t>
-        </is>
-      </c>
-      <c r="D406" t="inlineStr"/>
+          <t>Transfer agent and filing fees</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E406" t="inlineStr">
         <is>
           <t>-</t>
@@ -49291,10 +49305,10 @@
         </is>
       </c>
       <c r="G406" s="5" t="n">
-        <v>2e-08</v>
+        <v>0.005619</v>
       </c>
       <c r="H406" s="5" t="n">
-        <v>0</v>
+        <v>0.009371000000000001</v>
       </c>
       <c r="I406" t="inlineStr">
         <is>
@@ -49370,12 +49384,12 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Shares                     Reserve                       Equity</t>
+          <t>Share‐based compensation                                          76,300                        ‐</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Dividends Declared ‐ ‐ ‐</t>
+          <t>Share‐based compensation                                          76,300                        ‐ total</t>
         </is>
       </c>
       <c r="D407" t="inlineStr"/>
@@ -49390,10 +49404,10 @@
         </is>
       </c>
       <c r="G407" s="5" t="n">
-        <v>-2.607051</v>
+        <v>0.212873</v>
       </c>
       <c r="H407" s="5" t="n">
-        <v>-2.607051</v>
+        <v>0.259507</v>
       </c>
       <c r="I407" t="inlineStr">
         <is>
@@ -49469,17 +49483,17 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Shares                     Reserve                       Equity</t>
+          <t>Share‐based compensation                                          76,300                        ‐</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss ‐ ‐ ‐</t>
+          <t>Loss before income taxes</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>PretaxIncome</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
@@ -49493,10 +49507,10 @@
         </is>
       </c>
       <c r="G408" s="5" t="n">
-        <v>-0.092471</v>
+        <v>-0.194593</v>
       </c>
       <c r="H408" s="5" t="n">
-        <v>-0.092471</v>
+        <v>-0.258622</v>
       </c>
       <c r="I408" t="inlineStr">
         <is>
@@ -49572,15 +49586,19 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Shares                     Reserve                       Equity</t>
+          <t>Tax recovery                                                                                           ‐           54,747</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Balance, March 31, 2012 2,606,303 7,980,827 383,173</t>
-        </is>
-      </c>
-      <c r="D409" t="inlineStr"/>
+          <t>Net loss from continuing operations</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E409" t="inlineStr">
         <is>
           <t>-</t>
@@ -49592,10 +49610,10 @@
         </is>
       </c>
       <c r="G409" s="5" t="n">
-        <v>0.0057</v>
+        <v>-0.139846</v>
       </c>
       <c r="H409" s="5" t="n">
-        <v>-8.3583</v>
+        <v>-0.258622</v>
       </c>
       <c r="I409" t="inlineStr">
         <is>
@@ -49671,12 +49689,12 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Share‐based payments                                ‐                    ‐        76,300                    ‐         76,300</t>
+          <t>Income from discontinued operations                                                   ‐           47,375</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss ‐ ‐ ‐</t>
+          <t>Loss and comprehensive loss $</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
@@ -49695,7 +49713,7 @@
         </is>
       </c>
       <c r="G410" s="5" t="n">
-        <v>-0.258622</v>
+        <v>-0.092471</v>
       </c>
       <c r="H410" s="5" t="n">
         <v>-0.258622</v>
@@ -49761,6 +49779,905 @@
         </is>
       </c>
       <c r="U410" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>Income from discontinued operations                                                   ‐           47,375</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>Weighted average number of shares outstanding</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G411" s="5" t="n">
+        <v>2.606303</v>
+      </c>
+      <c r="H411" s="5" t="n">
+        <v>10.989865</v>
+      </c>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>Income from discontinued operations                                                   ‐           47,375</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>Basic and diluted loss per share, continuing operations $</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr"/>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G412" s="5" t="n">
+        <v>-5e-08</v>
+      </c>
+      <c r="H412" s="5" t="n">
+        <v>-2e-08</v>
+      </c>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>Income from discontinued operations                                                   ‐           47,375</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>Basic and diluted loss per share, discontinued operations $</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr"/>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G413" s="5" t="n">
+        <v>2e-08</v>
+      </c>
+      <c r="H413" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>Shares                     Reserve                       Equity</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>Dividends Declared ‐ ‐ ‐</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr"/>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G414" s="5" t="n">
+        <v>-2.607051</v>
+      </c>
+      <c r="H414" s="5" t="n">
+        <v>-2.607051</v>
+      </c>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>Shares                     Reserve                       Equity</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>Loss and comprehensive loss ‐ ‐ ‐</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G415" s="5" t="n">
+        <v>-0.092471</v>
+      </c>
+      <c r="H415" s="5" t="n">
+        <v>-0.092471</v>
+      </c>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>Shares                     Reserve                       Equity</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>Balance, March 31, 2012 2,606,303 7,980,827 383,173</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr"/>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G416" s="5" t="n">
+        <v>0.0057</v>
+      </c>
+      <c r="H416" s="5" t="n">
+        <v>-8.3583</v>
+      </c>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>Share‐based payments                                ‐                    ‐        76,300                    ‐         76,300</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>Loss and comprehensive loss ‐ ‐ ‐</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G417" s="5" t="n">
+        <v>-0.258622</v>
+      </c>
+      <c r="H417" s="5" t="n">
+        <v>-0.258622</v>
+      </c>
+      <c r="I417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>Loss before income taxes                                          (194,593)           (1,231,974)</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>Tax recovery (expense) (note</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr"/>
+      <c r="E418" s="5" t="n">
+        <v>-2.444624</v>
+      </c>
+      <c r="F418" s="5" t="n">
+        <v>0.054747</v>
+      </c>
+      <c r="G418" s="5" t="n">
+        <v>9e-06</v>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>Net loss from continuing operations                                 (139,846)           (3,676,598)</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>Income from discontinued operations (note</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr"/>
+      <c r="E419" s="5" t="n">
+        <v>0.973399</v>
+      </c>
+      <c r="F419" s="5" t="n">
+        <v>0.047375</v>
+      </c>
+      <c r="G419" s="5" t="n">
+        <v>7e-06</v>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U419" t="inlineStr">
         <is>
           <t>-</t>
         </is>
